--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 13/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +203 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +153 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="B29" s="20" t="n">
-        <v>0.049</v>
+        <v>0.0534</v>
       </c>
     </row>
     <row r="30">

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
+++ b/docs/dossiers/dossier-saint-maur-des-fosses-4dc16ba0.xlsx
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +153 €/mois.</t>
+          <t>EN CLAIR — Loyer inconnu à ce stade : le dossier est pré-rempli côté acquisition ; renseignez le loyer (feuille Synthèse) pour activer tous les calculs.</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Murs libres — local à louer après l'achat</t>
+          <t>Murs occupés — un locataire en place paie déjà un loyer</t>
         </is>
       </c>
     </row>
@@ -990,14 +990,7 @@
           <t>Loyer mensuel HT</t>
         </is>
       </c>
-      <c r="B20" s="18" t="n">
-        <v>1830</v>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>ESTIMATION au loyer de marché local — aucun bail ne le garantit</t>
-        </is>
-      </c>
+      <c r="B20" s="18" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -1404,7 +1397,7 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>68/100</t>
+          <t>74/100</t>
         </is>
       </c>
       <c r="C58" s="19" t="inlineStr">
@@ -2254,7 +2247,7 @@
       </c>
       <c r="B6" s="29" t="inlineStr">
         <is>
-          <t>Murs libres</t>
+          <t>Murs occupés</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2307,7 @@
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>loyer_estime</t>
+          <t>aucune</t>
         </is>
       </c>
     </row>
